--- a/artfynd/A 55823-2024 artfynd.xlsx
+++ b/artfynd/A 55823-2024 artfynd.xlsx
@@ -5527,7 +5527,7 @@
         <v>119231117</v>
       </c>
       <c r="B45" t="n">
-        <v>90183</v>
+        <v>90193</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 55823-2024 artfynd.xlsx
+++ b/artfynd/A 55823-2024 artfynd.xlsx
@@ -5527,7 +5527,7 @@
         <v>119231117</v>
       </c>
       <c r="B45" t="n">
-        <v>90193</v>
+        <v>90205</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 55823-2024 artfynd.xlsx
+++ b/artfynd/A 55823-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119179457</v>
       </c>
       <c r="B2" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellantjärnsbodarna (Mellantjärnsbodarna), Mpd</t>
+          <t>Mellantjärnsbodarna, Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 55823-2024 artfynd.xlsx
+++ b/artfynd/A 55823-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119179457</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55823-2024 artfynd.xlsx
+++ b/artfynd/A 55823-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119179457</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
